--- a/psychopy_exp_files/sequences/learning_block3_fixed-middle-10_12.xlsx
+++ b/psychopy_exp_files/sequences/learning_block3_fixed-middle-10_12.xlsx
@@ -564,37 +564,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_46.jpg</t>
+          <t>stimuli/phone/phone_30.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_47.jpg</t>
+          <t>stimuli/key/key_19.jpg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_20.jpg</t>
+          <t>stimuli/hand/hand_31.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>key</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -632,13 +632,13 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="W2" t="n">
         <v>2</v>
@@ -663,84 +663,84 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_47.jpg</t>
+          <t>stimuli/key/key_19.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_32.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>stimuli/key/key_26.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>key</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.53</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.25</v>
+        <v>0.42</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S3" t="n">
         <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="U3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W3" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -762,52 +762,52 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_19.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>stimuli/car/car_06.jpg</t>
+          <t>stimuli/pencil/pencil_35.jpg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -816,30 +816,30 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S4" t="n">
         <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -861,84 +861,84 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_15.jpg</t>
+          <t>stimuli/jacket/jacket_07.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_32.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_41.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P5" t="n">
         <v>0.64</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S5" t="n">
         <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -960,84 +960,84 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_15.jpg</t>
+          <t>stimuli/jacket/jacket_07.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_47.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_15.jpg</t>
+          <t>stimuli/hammer/hammer_38.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>stimuli/car/car_06.jpg</t>
+          <t>stimuli/fish/fish_39.jpg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q6" t="n">
         <v>0.47</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -1059,44 +1059,44 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_47.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_19.jpg</t>
+          <t>stimuli/hammer/hammer_38.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_46.jpg</t>
+          <t>stimuli/phone/phone_30.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>ball</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>pencil</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>left</t>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1127,16 +1127,16 @@
         <v>7</v>
       </c>
       <c r="T7" t="n">
+        <v>6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>7</v>
+      </c>
+      <c r="V7" t="n">
+        <v>17</v>
+      </c>
+      <c r="W7" t="n">
         <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>4</v>
-      </c>
-      <c r="V7" t="n">
-        <v>16</v>
-      </c>
-      <c r="W7" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1158,84 +1158,84 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_19.jpg</t>
+          <t>stimuli/hammer/hammer_38.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_15.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_20.jpg</t>
+          <t>stimuli/fish/fish_39.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/jacket/jacket_07.jpg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fish</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.75</v>
+        <v>0.58</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S8" t="n">
         <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U8" t="n">
+        <v>5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>12</v>
+      </c>
+      <c r="W8" t="n">
         <v>10</v>
-      </c>
-      <c r="V8" t="n">
-        <v>3</v>
-      </c>
-      <c r="W8" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -1257,42 +1257,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_15.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_32.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_15.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1325,16 +1325,16 @@
         <v>9</v>
       </c>
       <c r="T9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="W9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -1356,42 +1356,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_32.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_20.jpg</t>
+          <t>stimuli/hand/hand_31.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_46.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_47.jpg</t>
+          <t>stimuli/key/key_19.jpg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>pencil</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.27</v>
+        <v>0.53</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1424,16 +1424,16 @@
         <v>10</v>
       </c>
       <c r="T10" t="n">
+        <v>9</v>
+      </c>
+      <c r="U10" t="n">
         <v>8</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>3</v>
       </c>
-      <c r="V10" t="n">
-        <v>16</v>
-      </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -1455,84 +1455,84 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_20.jpg</t>
+          <t>stimuli/hand/hand_31.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_41.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_47.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_15.jpg</t>
+          <t>stimuli/hammer/hammer_38.jpg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4</v>
+        <v>0.27</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S11" t="n">
         <v>11</v>
       </c>
       <c r="T11" t="n">
+        <v>8</v>
+      </c>
+      <c r="U11" t="n">
         <v>3</v>
       </c>
-      <c r="U11" t="n">
-        <v>6</v>
-      </c>
       <c r="V11" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="W11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -1554,27 +1554,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_41.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_46.jpg</t>
+          <t>stimuli/phone/phone_30.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/jacket/jacket_07.jpg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1599,19 +1599,19 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P12" t="n">
         <v>0.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -1622,16 +1622,16 @@
         <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
         <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -1653,22 +1653,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>stimuli/car/car_06.jpg</t>
+          <t>stimuli/fish/fish_39.jpg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/pencil/pencil_35.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_20.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1678,19 +1678,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>pencil</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>left</t>
@@ -1698,19 +1698,19 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -1724,13 +1724,13 @@
         <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V13" t="n">
+        <v>16</v>
+      </c>
+      <c r="W13" t="n">
         <v>9</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1752,42 +1752,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>stimuli/car/car_06.jpg</t>
+          <t>stimuli/fish/fish_39.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>stimuli/key/key_26.jpg</t>
+          <t>stimuli/pencil/pencil_35.jpg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_47.jpg</t>
+          <t>stimuli/key/key_19.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_47.jpg</t>
+          <t>stimuli/hand/hand_31.jpg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>pencil</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>key</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1809,7 +1809,7 @@
         <v>0.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.53</v>
+        <v>0.27</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -1820,16 +1820,16 @@
         <v>14</v>
       </c>
       <c r="T14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U14" t="n">
+        <v>16</v>
+      </c>
+      <c r="V14" t="n">
         <v>15</v>
       </c>
-      <c r="V14" t="n">
-        <v>17</v>
-      </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -1851,84 +1851,84 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_03.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_15.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q15" t="n">
         <v>0.31</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U15" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1950,42 +1950,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -2018,16 +2018,16 @@
         <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W16" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -2049,37 +2049,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2103,27 +2103,27 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q17" t="n">
         <v>0.36</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S17" t="n">
         <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V17" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W17" t="n">
         <v>15</v>
@@ -2148,47 +2148,47 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2198,34 +2198,34 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P18" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="Q18" t="n">
         <v>0.53</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0.36</v>
-      </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S18" t="n">
         <v>5</v>
       </c>
       <c r="T18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W18" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -2247,84 +2247,84 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.64</v>
+        <v>0.47</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S19" t="n">
         <v>6</v>
       </c>
       <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
         <v>10</v>
       </c>
-      <c r="U19" t="n">
-        <v>5</v>
-      </c>
       <c r="V19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -2346,32 +2346,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/house/house_32.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_15.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2396,34 +2396,34 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.58</v>
+        <v>0.4</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S20" t="n">
         <v>7</v>
       </c>
       <c r="T20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="V20" t="n">
         <v>9</v>
       </c>
       <c r="W20" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -2445,47 +2445,47 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stimuli/house/house_32.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2495,34 +2495,34 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0.53</v>
+        <v>0.33</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S21" t="n">
         <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U21" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="W21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -2544,27 +2544,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>stimuli/house/house_32.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_03.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2584,41 +2584,41 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S22" t="n">
         <v>9</v>
       </c>
       <c r="T22" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
         <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="W22" t="n">
         <v>10</v>
@@ -2643,22 +2643,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2668,17 +2668,17 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2688,19 +2688,19 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P23" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="Q23" t="n">
         <v>0.53</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0.27</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -2714,13 +2714,13 @@
         <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V23" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="W23" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -2742,84 +2742,84 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_15.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0.8</v>
+        <v>0.47</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S24" t="n">
         <v>11</v>
       </c>
       <c r="T24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V24" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="W24" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
@@ -2841,84 +2841,84 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_15.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_03.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P25" t="n">
         <v>0.73</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S25" t="n">
         <v>12</v>
       </c>
       <c r="T25" t="n">
+        <v>7</v>
+      </c>
+      <c r="U25" t="n">
         <v>4</v>
       </c>
-      <c r="U25" t="n">
-        <v>7</v>
-      </c>
       <c r="V25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -2940,27 +2940,27 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_15.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>stimuli/house/house_32.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3008,16 +3008,16 @@
         <v>13</v>
       </c>
       <c r="T26" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U26" t="n">
         <v>15</v>
       </c>
       <c r="V26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W26" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -3039,22 +3039,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3064,27 +3064,27 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t>guitar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>pencil</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -3093,14 +3093,14 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S27" t="n">
@@ -3110,13 +3110,13 @@
         <v>15</v>
       </c>
       <c r="U27" t="n">
+        <v>13</v>
+      </c>
+      <c r="V27" t="n">
         <v>16</v>
       </c>
-      <c r="V27" t="n">
-        <v>1</v>
-      </c>
       <c r="W27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -3138,57 +3138,57 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_46.jpg</t>
+          <t>stimuli/phone/phone_30.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_47.jpg</t>
+          <t>stimuli/key/key_19.jpg</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_20.jpg</t>
+          <t>stimuli/hand/hand_31.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>stimuli/car/car_06.jpg</t>
+          <t>stimuli/fish/fish_39.jpg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>key</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -3199,23 +3199,23 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S28" t="n">
         <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U28" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V28" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="W28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
@@ -3237,52 +3237,52 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_47.jpg</t>
+          <t>stimuli/key/key_19.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_15.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>stimuli/key/key_26.jpg</t>
+          <t>stimuli/pencil/pencil_35.jpg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>key</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3298,23 +3298,23 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S29" t="n">
         <v>3</v>
       </c>
       <c r="T29" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="U29" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
@@ -3336,39 +3336,39 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_47.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>bicycle</t>
@@ -3376,41 +3376,41 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.75</v>
+        <v>0.58</v>
       </c>
       <c r="Q30" t="n">
         <v>0.42</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S30" t="n">
         <v>4</v>
       </c>
       <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4</v>
+      </c>
+      <c r="V30" t="n">
         <v>9</v>
-      </c>
-      <c r="U30" t="n">
-        <v>7</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1</v>
       </c>
       <c r="W30" t="n">
         <v>2</v>
@@ -3435,39 +3435,39 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_15.jpg</t>
+          <t>stimuli/jacket/jacket_07.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_19.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_47.jpg</t>
+          <t>stimuli/phone/phone_30.jpg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>phone</t>
@@ -3475,12 +3475,12 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3489,27 +3489,27 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S31" t="n">
         <v>5</v>
       </c>
       <c r="T31" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U31" t="n">
+        <v>10</v>
+      </c>
+      <c r="V31" t="n">
         <v>5</v>
-      </c>
-      <c r="V31" t="n">
-        <v>4</v>
       </c>
       <c r="W31" t="n">
         <v>17</v>
@@ -3534,84 +3534,84 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_15.jpg</t>
+          <t>stimuli/jacket/jacket_07.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_47.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_32.jpg</t>
+          <t>stimuli/hammer/hammer_38.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>stimuli/car/car_06.jpg</t>
+          <t>stimuli/pencil/pencil_35.jpg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S32" t="n">
         <v>6</v>
       </c>
       <c r="T32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W32" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
@@ -3633,42 +3633,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_47.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_19.jpg</t>
+          <t>stimuli/hammer/hammer_38.jpg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_41.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>stimuli/key/key_26.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3678,19 +3678,19 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P33" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Q33" t="n">
         <v>0.64</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0.47</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
@@ -3701,16 +3701,16 @@
         <v>7</v>
       </c>
       <c r="T33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U33" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V33" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W33" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -3732,47 +3732,47 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_19.jpg</t>
+          <t>stimuli/hammer/hammer_38.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_15.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_47.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_15.jpg</t>
+          <t>stimuli/jacket/jacket_07.jpg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3782,34 +3782,34 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="Q34" t="n">
         <v>0.2</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S34" t="n">
         <v>8</v>
       </c>
       <c r="T34" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U34" t="n">
+        <v>5</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
         <v>10</v>
-      </c>
-      <c r="V34" t="n">
-        <v>17</v>
-      </c>
-      <c r="W34" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -3831,84 +3831,84 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_15.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_32.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_20.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/key/key_19.jpg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S35" t="n">
         <v>9</v>
       </c>
       <c r="T35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W35" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36">
@@ -3930,42 +3930,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_32.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_20.jpg</t>
+          <t>stimuli/hand/hand_31.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_41.jpg</t>
+          <t>stimuli/fish/fish_39.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_46.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
@@ -3998,16 +3998,16 @@
         <v>10</v>
       </c>
       <c r="T36" t="n">
+        <v>9</v>
+      </c>
+      <c r="U36" t="n">
         <v>8</v>
       </c>
-      <c r="U36" t="n">
-        <v>3</v>
-      </c>
       <c r="V36" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="W36" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -4029,84 +4029,84 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_20.jpg</t>
+          <t>stimuli/hand/hand_31.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_41.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_47.jpg</t>
+          <t>stimuli/phone/phone_30.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S37" t="n">
         <v>11</v>
       </c>
       <c r="T37" t="n">
+        <v>8</v>
+      </c>
+      <c r="U37" t="n">
         <v>3</v>
-      </c>
-      <c r="U37" t="n">
-        <v>6</v>
       </c>
       <c r="V37" t="n">
         <v>17</v>
       </c>
       <c r="W37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
@@ -4128,27 +4128,27 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_41.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/pencil/pencil_35.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_19.jpg</t>
+          <t>stimuli/hammer/hammer_38.jpg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4158,17 +4158,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t>pencil</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t>hammer</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4178,34 +4178,34 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="Q38" t="n">
         <v>0.33</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S38" t="n">
         <v>12</v>
       </c>
       <c r="T38" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U38" t="n">
         <v>2</v>
       </c>
       <c r="V38" t="n">
+        <v>16</v>
+      </c>
+      <c r="W38" t="n">
         <v>7</v>
-      </c>
-      <c r="W38" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -4227,22 +4227,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>stimuli/car/car_06.jpg</t>
+          <t>stimuli/fish/fish_39.jpg</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_46.jpg</t>
+          <t>stimuli/phone/phone_30.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_47.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4252,27 +4252,27 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4284,11 +4284,11 @@
         <v>0.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S39" t="n">
@@ -4298,13 +4298,13 @@
         <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V39" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W39" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -4326,57 +4326,57 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>stimuli/car/car_06.jpg</t>
+          <t>stimuli/fish/fish_39.jpg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>stimuli/key/key_26.jpg</t>
+          <t>stimuli/pencil/pencil_35.jpg</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_15.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_46.jpg</t>
+          <t>stimuli/phone/phone_30.jpg</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -4387,23 +4387,23 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S40" t="n">
         <v>14</v>
       </c>
       <c r="T40" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U40" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W40" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41">
@@ -4425,44 +4425,44 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_03.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>center</t>
@@ -4470,19 +4470,19 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0.36</v>
+        <v>0.8</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
@@ -4493,16 +4493,16 @@
         <v>2</v>
       </c>
       <c r="T41" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U41" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V41" t="n">
+        <v>6</v>
+      </c>
+      <c r="W41" t="n">
         <v>4</v>
-      </c>
-      <c r="W41" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="42">
@@ -4524,47 +4524,47 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -4585,23 +4585,23 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S42" t="n">
         <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W42" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43">
@@ -4623,52 +4623,52 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_15.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4684,23 +4684,23 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S43" t="n">
         <v>4</v>
       </c>
       <c r="T43" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U43" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W43" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -4722,32 +4722,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4790,10 +4790,10 @@
         <v>5</v>
       </c>
       <c r="T44" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V44" t="n">
         <v>2</v>
@@ -4821,57 +4821,57 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_03.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -4882,23 +4882,23 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S45" t="n">
         <v>6</v>
       </c>
       <c r="T45" t="n">
+        <v>5</v>
+      </c>
+      <c r="U45" t="n">
         <v>10</v>
       </c>
-      <c r="U45" t="n">
-        <v>5</v>
-      </c>
       <c r="V45" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W45" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
@@ -4920,84 +4920,84 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.33</v>
+        <v>0.64</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S46" t="n">
         <v>7</v>
       </c>
       <c r="T46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U46" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="V46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W46" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
@@ -5019,47 +5019,47 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>stimuli/house/house_32.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5069,34 +5069,34 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="Q47" t="n">
         <v>0.27</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S47" t="n">
         <v>8</v>
       </c>
       <c r="T47" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U47" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V47" t="n">
         <v>4</v>
       </c>
       <c r="W47" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -5118,27 +5118,27 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>stimuli/house/house_32.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_15.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
@@ -5186,13 +5186,13 @@
         <v>9</v>
       </c>
       <c r="T48" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U48" t="n">
         <v>2</v>
       </c>
       <c r="V48" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="W48" t="n">
         <v>5</v>
@@ -5217,22 +5217,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5242,22 +5242,22 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S49" t="n">
@@ -5288,13 +5288,13 @@
         <v>2</v>
       </c>
       <c r="U49" t="n">
+        <v>9</v>
+      </c>
+      <c r="V49" t="n">
+        <v>3</v>
+      </c>
+      <c r="W49" t="n">
         <v>8</v>
-      </c>
-      <c r="V49" t="n">
-        <v>6</v>
-      </c>
-      <c r="W49" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -5316,42 +5316,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>stimuli/house/house_32.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5370,10 +5370,10 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
@@ -5384,16 +5384,16 @@
         <v>11</v>
       </c>
       <c r="T50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U50" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V50" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
@@ -5415,84 +5415,84 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_15.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_03.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.47</v>
+        <v>0.27</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S51" t="n">
         <v>12</v>
       </c>
       <c r="T51" t="n">
+        <v>7</v>
+      </c>
+      <c r="U51" t="n">
         <v>4</v>
       </c>
-      <c r="U51" t="n">
-        <v>7</v>
-      </c>
       <c r="V51" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W51" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -5514,27 +5514,27 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_15.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>stimuli/house/house_32.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5568,10 +5568,10 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
@@ -5582,16 +5582,16 @@
         <v>13</v>
       </c>
       <c r="T52" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U52" t="n">
         <v>15</v>
       </c>
       <c r="V52" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="W52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53">
@@ -5613,22 +5613,22 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5638,17 +5638,17 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t>guitar</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t>pencil</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>car</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5670,7 +5670,7 @@
         <v>0.8</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
@@ -5684,13 +5684,13 @@
         <v>15</v>
       </c>
       <c r="U53" t="n">
+        <v>13</v>
+      </c>
+      <c r="V53" t="n">
         <v>16</v>
       </c>
-      <c r="V53" t="n">
-        <v>11</v>
-      </c>
       <c r="W53" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -5712,84 +5712,84 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_46.jpg</t>
+          <t>stimuli/phone/phone_30.jpg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_47.jpg</t>
+          <t>stimuli/key/key_19.jpg</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_32.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>stimuli/key/key_26.jpg</t>
+          <t>stimuli/fish/fish_39.jpg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>key</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0.47</v>
+        <v>0.36</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S54" t="n">
         <v>2</v>
       </c>
       <c r="T54" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U54" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V54" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="W54" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55">
@@ -5811,32 +5811,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_47.jpg</t>
+          <t>stimuli/key/key_19.jpg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_19.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>stimuli/car/car_06.jpg</t>
+          <t>stimuli/pencil/pencil_35.jpg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>key</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5856,19 +5856,19 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
@@ -5879,16 +5879,16 @@
         <v>3</v>
       </c>
       <c r="T55" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="U55" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V55" t="n">
         <v>4</v>
       </c>
       <c r="W55" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56">
@@ -5910,37 +5910,37 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_15.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5955,16 +5955,16 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q56" t="n">
         <v>0.42</v>
@@ -5978,13 +5978,13 @@
         <v>4</v>
       </c>
       <c r="T56" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W56" t="n">
         <v>2</v>
@@ -6009,42 +6009,42 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_15.jpg</t>
+          <t>stimuli/jacket/jacket_07.jpg</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_47.jpg</t>
+          <t>stimuli/hand/hand_31.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>stimuli/key/key_26.jpg</t>
+          <t>stimuli/pencil/pencil_35.jpg</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6054,16 +6054,16 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="Q57" t="n">
         <v>0.36</v>
@@ -6077,16 +6077,16 @@
         <v>5</v>
       </c>
       <c r="T57" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V57" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W57" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58">
@@ -6108,42 +6108,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_15.jpg</t>
+          <t>stimuli/jacket/jacket_07.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_47.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_15.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_41.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6153,12 +6153,12 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P58" t="n">
@@ -6176,16 +6176,16 @@
         <v>6</v>
       </c>
       <c r="T58" t="n">
+        <v>10</v>
+      </c>
+      <c r="U58" t="n">
+        <v>6</v>
+      </c>
+      <c r="V58" t="n">
         <v>5</v>
       </c>
-      <c r="U58" t="n">
-        <v>1</v>
-      </c>
-      <c r="V58" t="n">
-        <v>10</v>
-      </c>
       <c r="W58" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -6207,84 +6207,84 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_47.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_19.jpg</t>
+          <t>stimuli/hammer/hammer_38.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_20.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>stimuli/car/car_06.jpg</t>
+          <t>stimuli/fish/fish_39.jpg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="Q59" t="n">
         <v>0.53</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S59" t="n">
         <v>7</v>
       </c>
       <c r="T59" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U59" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V59" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W59" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60">
@@ -6306,44 +6306,44 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_19.jpg</t>
+          <t>stimuli/hammer/hammer_38.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_15.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/key/key_19.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_15.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="M60" t="inlineStr">
         <is>
           <t>left</t>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
@@ -6374,16 +6374,16 @@
         <v>8</v>
       </c>
       <c r="T60" t="n">
+        <v>7</v>
+      </c>
+      <c r="U60" t="n">
+        <v>5</v>
+      </c>
+      <c r="V60" t="n">
+        <v>15</v>
+      </c>
+      <c r="W60" t="n">
         <v>4</v>
-      </c>
-      <c r="U60" t="n">
-        <v>10</v>
-      </c>
-      <c r="V60" t="n">
-        <v>9</v>
-      </c>
-      <c r="W60" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="61">
@@ -6405,47 +6405,47 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_15.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_32.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_46.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/jacket/jacket_07.jpg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>pencil</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6455,34 +6455,34 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0.53</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.4</v>
+        <v>0.27</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S61" t="n">
         <v>9</v>
       </c>
       <c r="T61" t="n">
+        <v>5</v>
+      </c>
+      <c r="U61" t="n">
+        <v>9</v>
+      </c>
+      <c r="V61" t="n">
+        <v>2</v>
+      </c>
+      <c r="W61" t="n">
         <v>10</v>
-      </c>
-      <c r="U61" t="n">
-        <v>8</v>
-      </c>
-      <c r="V61" t="n">
-        <v>16</v>
-      </c>
-      <c r="W61" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="62">
@@ -6504,42 +6504,42 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_32.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_20.jpg</t>
+          <t>stimuli/hand/hand_31.jpg</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>stimuli/key/key_26.jpg</t>
+          <t>stimuli/pencil/pencil_35.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_47.jpg</t>
+          <t>stimuli/hammer/hammer_38.jpg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6561,7 +6561,7 @@
         <v>0.64</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.53</v>
+        <v>0.2</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
@@ -6572,16 +6572,16 @@
         <v>10</v>
       </c>
       <c r="T62" t="n">
+        <v>9</v>
+      </c>
+      <c r="U62" t="n">
         <v>8</v>
       </c>
-      <c r="U62" t="n">
-        <v>3</v>
-      </c>
       <c r="V62" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W62" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63">
@@ -6603,47 +6603,47 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_20.jpg</t>
+          <t>stimuli/hand/hand_31.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_41.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_46.jpg</t>
+          <t>stimuli/phone/phone_30.jpg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/jacket/jacket_07.jpg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -6653,34 +6653,34 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P63" t="n">
         <v>0.67</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S63" t="n">
         <v>11</v>
       </c>
       <c r="T63" t="n">
+        <v>8</v>
+      </c>
+      <c r="U63" t="n">
         <v>3</v>
       </c>
-      <c r="U63" t="n">
-        <v>6</v>
-      </c>
       <c r="V63" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W63" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64">
@@ -6702,47 +6702,47 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_41.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>stimuli/car/car_06.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_32.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>car</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -6752,34 +6752,34 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S64" t="n">
         <v>12</v>
       </c>
       <c r="T64" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U64" t="n">
         <v>2</v>
       </c>
       <c r="V64" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="W64" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -6801,22 +6801,22 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>stimuli/car/car_06.jpg</t>
+          <t>stimuli/fish/fish_39.jpg</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/phone/phone_30.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_19.jpg</t>
+          <t>stimuli/hammer/hammer_38.jpg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6826,22 +6826,22 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -6851,18 +6851,18 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="Q65" t="n">
         <v>0.4</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S65" t="n">
@@ -6872,13 +6872,13 @@
         <v>2</v>
       </c>
       <c r="U65" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V65" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="W65" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
@@ -6900,84 +6900,84 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>stimuli/car/car_06.jpg</t>
+          <t>stimuli/fish/fish_39.jpg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>stimuli/key/key_26.jpg</t>
+          <t>stimuli/pencil/pencil_35.jpg</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_47.jpg</t>
+          <t>stimuli/jacket/jacket_07.jpg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_46.jpg</t>
+          <t>stimuli/phone/phone_30.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="Q66" t="n">
         <v>0.26</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S66" t="n">
         <v>14</v>
       </c>
       <c r="T66" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U66" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="W66" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67">
@@ -6999,84 +6999,84 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_03.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0.36</v>
+        <v>0.47</v>
       </c>
       <c r="Q67" t="n">
         <v>0.2</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S67" t="n">
         <v>2</v>
       </c>
       <c r="T67" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U67" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W67" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68">
@@ -7098,37 +7098,37 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -7159,20 +7159,20 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S68" t="n">
         <v>3</v>
       </c>
       <c r="T68" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="U68" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W68" t="n">
         <v>15</v>
@@ -7197,42 +7197,42 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7242,12 +7242,12 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -7265,16 +7265,16 @@
         <v>4</v>
       </c>
       <c r="T69" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U69" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V69" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W69" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70">
@@ -7296,37 +7296,37 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>stimuli/house/house_32.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7341,12 +7341,12 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P70" t="n">
@@ -7364,13 +7364,13 @@
         <v>5</v>
       </c>
       <c r="T70" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V70" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="W70" t="n">
         <v>15</v>
@@ -7395,37 +7395,37 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_15.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -7452,24 +7452,24 @@
         <v>0.8</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S71" t="n">
         <v>6</v>
       </c>
       <c r="T71" t="n">
+        <v>5</v>
+      </c>
+      <c r="U71" t="n">
         <v>10</v>
       </c>
-      <c r="U71" t="n">
-        <v>5</v>
-      </c>
       <c r="V71" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="W71" t="n">
         <v>7</v>
@@ -7494,84 +7494,84 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_03.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0.4</v>
+        <v>0.58</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.27</v>
+        <v>0.47</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S72" t="n">
         <v>7</v>
       </c>
       <c r="T72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U72" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="V72" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="W72" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73">
@@ -7593,44 +7593,44 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>stimuli/house/house_32.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="M73" t="inlineStr">
         <is>
           <t>right</t>
@@ -7647,10 +7647,10 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
@@ -7661,16 +7661,16 @@
         <v>8</v>
       </c>
       <c r="T73" t="n">
+        <v>8</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
+      </c>
+      <c r="V73" t="n">
+        <v>15</v>
+      </c>
+      <c r="W73" t="n">
         <v>3</v>
-      </c>
-      <c r="U73" t="n">
-        <v>9</v>
-      </c>
-      <c r="V73" t="n">
-        <v>2</v>
-      </c>
-      <c r="W73" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -7692,27 +7692,27 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>stimuli/house/house_32.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7737,19 +7737,19 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
@@ -7760,13 +7760,13 @@
         <v>9</v>
       </c>
       <c r="T74" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U74" t="n">
         <v>2</v>
       </c>
       <c r="V74" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="W74" t="n">
         <v>10</v>
@@ -7791,22 +7791,22 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_03.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7816,17 +7816,17 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>glasses</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
           <t>hand</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7848,7 +7848,7 @@
         <v>0.6</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
@@ -7862,13 +7862,13 @@
         <v>2</v>
       </c>
       <c r="U75" t="n">
+        <v>9</v>
+      </c>
+      <c r="V75" t="n">
+        <v>18</v>
+      </c>
+      <c r="W75" t="n">
         <v>8</v>
-      </c>
-      <c r="V75" t="n">
-        <v>17</v>
-      </c>
-      <c r="W75" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="76">
@@ -7890,84 +7890,84 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="Q76" t="n">
         <v>0.33</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S76" t="n">
         <v>11</v>
       </c>
       <c r="T76" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U76" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V76" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="W76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77">
@@ -7989,84 +7989,84 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_15.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_03.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S77" t="n">
         <v>12</v>
       </c>
       <c r="T77" t="n">
+        <v>7</v>
+      </c>
+      <c r="U77" t="n">
         <v>4</v>
       </c>
-      <c r="U77" t="n">
-        <v>7</v>
-      </c>
       <c r="V77" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W77" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
@@ -8088,27 +8088,27 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_15.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8142,10 +8142,10 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
@@ -8156,16 +8156,16 @@
         <v>13</v>
       </c>
       <c r="T78" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U78" t="n">
         <v>15</v>
       </c>
       <c r="V78" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="W78" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -8187,22 +8187,22 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8212,17 +8212,17 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t>guitar</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t>pencil</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>car</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -8232,19 +8232,19 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P79" t="n">
         <v>0.8</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
@@ -8258,13 +8258,13 @@
         <v>15</v>
       </c>
       <c r="U79" t="n">
+        <v>13</v>
+      </c>
+      <c r="V79" t="n">
         <v>16</v>
       </c>
-      <c r="V79" t="n">
-        <v>11</v>
-      </c>
       <c r="W79" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80">
@@ -8286,44 +8286,44 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_46.jpg</t>
+          <t>stimuli/phone/phone_30.jpg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_47.jpg</t>
+          <t>stimuli/key/key_19.jpg</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_15.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>stimuli/key/key_26.jpg</t>
+          <t>stimuli/pencil/pencil_35.jpg</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
           <t>pencil</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
       <c r="M80" t="inlineStr">
         <is>
           <t>right</t>
@@ -8331,16 +8331,16 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0.53</v>
+        <v>0.36</v>
       </c>
       <c r="Q80" t="n">
         <v>0.2</v>
@@ -8354,16 +8354,16 @@
         <v>2</v>
       </c>
       <c r="T80" t="n">
+        <v>17</v>
+      </c>
+      <c r="U80" t="n">
+        <v>15</v>
+      </c>
+      <c r="V80" t="n">
+        <v>3</v>
+      </c>
+      <c r="W80" t="n">
         <v>16</v>
-      </c>
-      <c r="U80" t="n">
-        <v>17</v>
-      </c>
-      <c r="V80" t="n">
-        <v>10</v>
-      </c>
-      <c r="W80" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="81">
@@ -8385,37 +8385,37 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_47.jpg</t>
+          <t>stimuli/key/key_19.jpg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_20.jpg</t>
+          <t>stimuli/hand/hand_31.jpg</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>key</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8430,12 +8430,12 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -8453,13 +8453,13 @@
         <v>3</v>
       </c>
       <c r="T81" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="U81" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V81" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="W81" t="n">
         <v>2</v>
@@ -8484,42 +8484,42 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_47.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>stimuli/car/car_06.jpg</t>
+          <t>stimuli/fish/fish_39.jpg</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -8538,7 +8538,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="Q82" t="n">
         <v>0.36</v>
@@ -8552,16 +8552,16 @@
         <v>4</v>
       </c>
       <c r="T82" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U82" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83">
@@ -8583,47 +8583,47 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_15.jpg</t>
+          <t>stimuli/jacket/jacket_07.jpg</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_32.jpg</t>
+          <t>stimuli/hammer/hammer_38.jpg</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>stimuli/key/key_26.jpg</t>
+          <t>stimuli/pencil/pencil_35.jpg</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t>hammer</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -8633,34 +8633,34 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="Q83" t="n">
         <v>0.36</v>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S83" t="n">
         <v>5</v>
       </c>
       <c r="T83" t="n">
+        <v>4</v>
+      </c>
+      <c r="U83" t="n">
+        <v>10</v>
+      </c>
+      <c r="V83" t="n">
         <v>7</v>
       </c>
-      <c r="U83" t="n">
-        <v>5</v>
-      </c>
-      <c r="V83" t="n">
-        <v>8</v>
-      </c>
       <c r="W83" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="84">
@@ -8682,84 +8682,84 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_15.jpg</t>
+          <t>stimuli/jacket/jacket_07.jpg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_47.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_20.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_46.jpg</t>
+          <t>stimuli/phone/phone_30.jpg</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q84" t="n">
         <v>0.33</v>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S84" t="n">
         <v>6</v>
       </c>
       <c r="T84" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U84" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V84" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W84" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85">
@@ -8781,84 +8781,84 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_47.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_19.jpg</t>
+          <t>stimuli/hammer/hammer_38.jpg</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_41.jpg</t>
+          <t>stimuli/phone/phone_30.jpg</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>stimuli/key/key_26.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
           <t>ball</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0.64</v>
+        <v>0.4</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.47</v>
+        <v>0.27</v>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S85" t="n">
         <v>7</v>
       </c>
       <c r="T85" t="n">
+        <v>6</v>
+      </c>
+      <c r="U85" t="n">
+        <v>7</v>
+      </c>
+      <c r="V85" t="n">
+        <v>17</v>
+      </c>
+      <c r="W85" t="n">
         <v>1</v>
-      </c>
-      <c r="U85" t="n">
-        <v>4</v>
-      </c>
-      <c r="V85" t="n">
-        <v>6</v>
-      </c>
-      <c r="W85" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="86">
@@ -8880,47 +8880,47 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_19.jpg</t>
+          <t>stimuli/hammer/hammer_38.jpg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_15.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/key/key_19.jpg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_15.jpg</t>
+          <t>stimuli/jacket/jacket_07.jpg</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -8930,34 +8930,34 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="Q86" t="n">
         <v>0.2</v>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S86" t="n">
         <v>8</v>
       </c>
       <c r="T86" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U86" t="n">
+        <v>5</v>
+      </c>
+      <c r="V86" t="n">
+        <v>15</v>
+      </c>
+      <c r="W86" t="n">
         <v>10</v>
-      </c>
-      <c r="V86" t="n">
-        <v>9</v>
-      </c>
-      <c r="W86" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="87">
@@ -8979,32 +8979,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_15.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_32.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_20.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_47.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -9014,49 +9014,49 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S87" t="n">
         <v>9</v>
       </c>
       <c r="T87" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U87" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V87" t="n">
         <v>3</v>
       </c>
       <c r="W87" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
@@ -9078,42 +9078,42 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_32.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_20.jpg</t>
+          <t>stimuli/hand/hand_31.jpg</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_15.jpg</t>
+          <t>stimuli/pencil/pencil_35.jpg</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_19.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -9132,10 +9132,10 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0.33</v>
+        <v>0.64</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R88" t="inlineStr">
         <is>
@@ -9146,16 +9146,16 @@
         <v>10</v>
       </c>
       <c r="T88" t="n">
+        <v>9</v>
+      </c>
+      <c r="U88" t="n">
         <v>8</v>
       </c>
-      <c r="U88" t="n">
-        <v>3</v>
-      </c>
       <c r="V88" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="W88" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89">
@@ -9177,47 +9177,47 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_20.jpg</t>
+          <t>stimuli/hand/hand_31.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_41.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_15.jpg</t>
+          <t>stimuli/pencil/pencil_35.jpg</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -9227,34 +9227,34 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0.47</v>
+        <v>0.8</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.2</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S89" t="n">
         <v>11</v>
       </c>
       <c r="T89" t="n">
+        <v>8</v>
+      </c>
+      <c r="U89" t="n">
         <v>3</v>
       </c>
-      <c r="U89" t="n">
-        <v>6</v>
-      </c>
       <c r="V89" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="W89" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="90">
@@ -9276,27 +9276,27 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_41.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_46.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_47.jpg</t>
+          <t>stimuli/jacket/jacket_07.jpg</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -9306,17 +9306,17 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -9326,34 +9326,34 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S90" t="n">
         <v>12</v>
       </c>
       <c r="T90" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U90" t="n">
         <v>2</v>
       </c>
       <c r="V90" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="W90" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91">
@@ -9375,22 +9375,22 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>stimuli/car/car_06.jpg</t>
+          <t>stimuli/fish/fish_39.jpg</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/phone/phone_30.jpg</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_32.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -9400,43 +9400,43 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P91" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q91" t="n">
         <v>0.67</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0.27</v>
-      </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S91" t="n">
@@ -9446,13 +9446,13 @@
         <v>2</v>
       </c>
       <c r="U91" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V91" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="W91" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -9474,47 +9474,47 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>stimuli/car/car_06.jpg</t>
+          <t>stimuli/fish/fish_39.jpg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>stimuli/key/key_26.jpg</t>
+          <t>stimuli/pencil/pencil_35.jpg</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_47.jpg</t>
+          <t>stimuli/key/key_19.jpg</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_19.jpg</t>
+          <t>stimuli/phone/phone_30.jpg</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t>pencil</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t>key</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -9524,34 +9524,34 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P92" t="n">
         <v>0.8</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.67</v>
+        <v>0.26</v>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S92" t="n">
         <v>14</v>
       </c>
       <c r="T92" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U92" t="n">
+        <v>16</v>
+      </c>
+      <c r="V92" t="n">
         <v>15</v>
       </c>
-      <c r="V92" t="n">
+      <c r="W92" t="n">
         <v>17</v>
-      </c>
-      <c r="W92" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="93">
@@ -9573,84 +9573,84 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_03.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="Q93" t="n">
         <v>0.2</v>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S93" t="n">
         <v>2</v>
       </c>
       <c r="T93" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U93" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W93" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="94">
@@ -9672,52 +9672,52 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -9726,30 +9726,30 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S94" t="n">
         <v>3</v>
       </c>
       <c r="T94" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="U94" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V94" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="W94" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95">
@@ -9771,47 +9771,47 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -9821,34 +9821,34 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S95" t="n">
         <v>4</v>
       </c>
       <c r="T95" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U95" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V95" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W95" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96">
@@ -9870,39 +9870,39 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_15.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>hammer</t>
@@ -9910,41 +9910,41 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S96" t="n">
         <v>5</v>
       </c>
       <c r="T96" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U96" t="n">
+        <v>5</v>
+      </c>
+      <c r="V96" t="n">
         <v>10</v>
-      </c>
-      <c r="V96" t="n">
-        <v>8</v>
       </c>
       <c r="W96" t="n">
         <v>7</v>
@@ -9969,37 +9969,37 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>stimuli/house/house_32.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -10014,16 +10014,16 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q97" t="n">
         <v>0.47</v>
@@ -10037,13 +10037,13 @@
         <v>6</v>
       </c>
       <c r="T97" t="n">
+        <v>5</v>
+      </c>
+      <c r="U97" t="n">
         <v>10</v>
       </c>
-      <c r="U97" t="n">
-        <v>5</v>
-      </c>
       <c r="V97" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W97" t="n">
         <v>15</v>
@@ -10068,37 +10068,37 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -10113,19 +10113,19 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="R98" t="inlineStr">
         <is>
@@ -10136,13 +10136,13 @@
         <v>7</v>
       </c>
       <c r="T98" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U98" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="V98" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="W98" t="n">
         <v>4</v>
@@ -10167,42 +10167,42 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>stimuli/house/house_32.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_03.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -10221,10 +10221,10 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.47</v>
+        <v>0.2</v>
       </c>
       <c r="R99" t="inlineStr">
         <is>
@@ -10235,16 +10235,16 @@
         <v>8</v>
       </c>
       <c r="T99" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U99" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V99" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W99" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
@@ -10266,27 +10266,27 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>stimuli/house/house_32.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -10296,54 +10296,54 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0.33</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S100" t="n">
         <v>9</v>
       </c>
       <c r="T100" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U100" t="n">
         <v>2</v>
       </c>
       <c r="V100" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W100" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101">
@@ -10365,22 +10365,22 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_03.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -10405,12 +10405,12 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -10422,11 +10422,11 @@
         <v>0.6</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S101" t="n">
@@ -10436,10 +10436,10 @@
         <v>2</v>
       </c>
       <c r="U101" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V101" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W101" t="n">
         <v>10</v>
@@ -10464,84 +10464,84 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S102" t="n">
         <v>11</v>
       </c>
       <c r="T102" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U102" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V102" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="W102" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
@@ -10563,84 +10563,84 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_15.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S103" t="n">
         <v>12</v>
       </c>
       <c r="T103" t="n">
+        <v>7</v>
+      </c>
+      <c r="U103" t="n">
         <v>4</v>
       </c>
-      <c r="U103" t="n">
-        <v>7</v>
-      </c>
       <c r="V103" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="W103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -10662,27 +10662,27 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_15.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_03.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -10692,54 +10692,54 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.4</v>
+        <v>0.53</v>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S104" t="n">
         <v>13</v>
       </c>
       <c r="T104" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U104" t="n">
         <v>15</v>
       </c>
       <c r="V104" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="W104" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
@@ -10761,22 +10761,22 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -10786,22 +10786,22 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -10811,18 +10811,18 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="Q105" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S105" t="n">
@@ -10832,13 +10832,13 @@
         <v>15</v>
       </c>
       <c r="U105" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="V105" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="W105" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/psychopy_exp_files/sequences/learning_block3_fixed-middle-10_12.xlsx
+++ b/psychopy_exp_files/sequences/learning_block3_fixed-middle-10_12.xlsx
@@ -574,12 +574,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -594,38 +594,38 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -638,10 +638,10 @@
         <v>16</v>
       </c>
       <c r="V2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -703,17 +703,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -724,7 +724,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -772,7 +772,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_49.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="Q4" t="n">
         <v>0.31</v>
@@ -836,7 +836,7 @@
         <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W4" t="n">
         <v>13</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_29.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -935,10 +935,10 @@
         <v>5</v>
       </c>
       <c r="V5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -975,7 +975,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1017,7 +1017,7 @@
         <v>0.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>8</v>
       </c>
       <c r="W6" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1094,17 +1094,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1116,11 +1116,11 @@
         <v>0.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1136,7 +1136,7 @@
         <v>18</v>
       </c>
       <c r="W7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1168,12 +1168,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_49.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_10.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1188,38 +1188,38 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S8" t="n">
@@ -1232,10 +1232,10 @@
         <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="W8" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>stimuli/key/key_11.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,17 +1287,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,18 +1307,18 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -1331,10 +1331,10 @@
         <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="W9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_10.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1430,10 +1430,10 @@
         <v>9</v>
       </c>
       <c r="V10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="W10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_26.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1584,38 +1584,38 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0.73</v>
+        <v>0.53</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.53</v>
+        <v>0.33</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S12" t="n">
@@ -1628,10 +1628,10 @@
         <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="W12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_10.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1707,10 +1707,10 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -1727,10 +1727,10 @@
         <v>15</v>
       </c>
       <c r="V13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_38.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1797,16 +1797,16 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.47</v>
+        <v>0.8</v>
       </c>
       <c r="Q14" t="n">
         <v>0.26</v>
@@ -1826,7 +1826,7 @@
         <v>13</v>
       </c>
       <c r="V14" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W14" t="n">
         <v>18</v>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_12.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_26.jpg</t>
+          <t>stimuli/pencil/pencil_35.jpg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1881,38 +1881,38 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.75</v>
+        <v>0.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S15" t="n">
@@ -1925,10 +1925,10 @@
         <v>15</v>
       </c>
       <c r="V15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_35.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0.42</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.25</v>
+        <v>0.36</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -2024,10 +2024,10 @@
         <v>1</v>
       </c>
       <c r="V16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W16" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_40.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/fish/fish_39.jpg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2079,38 +2079,38 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.75</v>
+        <v>0.47</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.47</v>
+        <v>0.36</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S17" t="n">
@@ -2123,10 +2123,10 @@
         <v>4</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W17" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_31.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_26.jpg</t>
+          <t>stimuli/pencil/pencil_35.jpg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2178,38 +2178,38 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.47</v>
+        <v>0.36</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S18" t="n">
@@ -2222,10 +2222,10 @@
         <v>10</v>
       </c>
       <c r="V18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W18" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2292,16 +2292,16 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="Q19" t="n">
         <v>0.47</v>
@@ -2321,7 +2321,7 @@
         <v>6</v>
       </c>
       <c r="V19" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W19" t="n">
         <v>12</v>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_14.jpg</t>
+          <t>stimuli/hand/hand_31.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2386,28 +2386,28 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q20" t="n">
         <v>0.47</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S20" t="n">
@@ -2420,7 +2420,7 @@
         <v>7</v>
       </c>
       <c r="V20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W20" t="n">
         <v>16</v>
@@ -2455,12 +2455,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/key/key_19.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_07.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2475,17 +2475,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2495,18 +2495,18 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S21" t="n">
@@ -2519,10 +2519,10 @@
         <v>5</v>
       </c>
       <c r="V21" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="W21" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/hand/hand_31.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_40.jpg</t>
+          <t>stimuli/phone/phone_30.jpg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2574,22 +2574,22 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2598,14 +2598,14 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.2</v>
+        <v>0.53</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S22" t="n">
@@ -2618,10 +2618,10 @@
         <v>9</v>
       </c>
       <c r="V22" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W22" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -2653,12 +2653,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_38.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2673,38 +2673,38 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0.8</v>
+        <v>0.47</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S23" t="n">
@@ -2717,10 +2717,10 @@
         <v>8</v>
       </c>
       <c r="V23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_40.jpg</t>
+          <t>stimuli/jacket/jacket_07.jpg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2777,12 +2777,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2792,18 +2792,18 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P24" t="n">
         <v>0.67</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S24" t="n">
@@ -2819,7 +2819,7 @@
         <v>17</v>
       </c>
       <c r="W24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/key/key_19.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_38.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2871,17 +2871,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2891,18 +2891,18 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S25" t="n">
@@ -2915,10 +2915,10 @@
         <v>2</v>
       </c>
       <c r="V25" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="W25" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_30.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/hammer/hammer_38.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2970,38 +2970,38 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S26" t="n">
@@ -3014,10 +3014,10 @@
         <v>12</v>
       </c>
       <c r="V26" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="W26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/key/key_19.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_07.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3069,17 +3069,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3089,18 +3089,18 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S27" t="n">
@@ -3113,10 +3113,10 @@
         <v>16</v>
       </c>
       <c r="V27" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="W27" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>stimuli/key/key_11.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3168,22 +3168,22 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3192,14 +3192,14 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S28" t="n">
@@ -3212,10 +3212,10 @@
         <v>16</v>
       </c>
       <c r="V28" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W28" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3272,33 +3272,33 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P29" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.25</v>
+        <v>0.42</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S29" t="n">
@@ -3314,7 +3314,7 @@
         <v>10</v>
       </c>
       <c r="W29" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -3346,12 +3346,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_49.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.42</v>
+        <v>0.31</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -3410,10 +3410,10 @@
         <v>3</v>
       </c>
       <c r="V30" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W30" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31">
@@ -3445,12 +3445,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_38.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_26.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3465,22 +3465,22 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3489,14 +3489,14 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S31" t="n">
@@ -3509,10 +3509,10 @@
         <v>5</v>
       </c>
       <c r="V31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S32" t="n">
@@ -3678,12 +3678,12 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_26.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3762,38 +3762,38 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S34" t="n">
@@ -3806,10 +3806,10 @@
         <v>1</v>
       </c>
       <c r="V34" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="W34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_10.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_29.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3861,17 +3861,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3881,18 +3881,18 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.47</v>
+        <v>0.75</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.2</v>
+        <v>0.53</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S35" t="n">
@@ -3905,10 +3905,10 @@
         <v>2</v>
       </c>
       <c r="V35" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="W35" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>stimuli/key/key_11.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3980,18 +3980,18 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S36" t="n">
@@ -4004,10 +4004,10 @@
         <v>9</v>
       </c>
       <c r="V36" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -4039,12 +4039,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_26.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4059,17 +4059,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4079,18 +4079,18 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.47</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S37" t="n">
@@ -4103,10 +4103,10 @@
         <v>7</v>
       </c>
       <c r="V37" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="W37" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>stimuli/key/key_11.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4158,17 +4158,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4178,18 +4178,18 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S38" t="n">
@@ -4202,10 +4202,10 @@
         <v>4</v>
       </c>
       <c r="V38" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_26.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4257,22 +4257,22 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4281,14 +4281,14 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.6</v>
+        <v>0.33</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S39" t="n">
@@ -4301,10 +4301,10 @@
         <v>15</v>
       </c>
       <c r="V39" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="W39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4376,18 +4376,18 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="Q40" t="n">
         <v>0.26</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S40" t="n">
@@ -4400,7 +4400,7 @@
         <v>13</v>
       </c>
       <c r="V40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W40" t="n">
         <v>18</v>
@@ -4465,17 +4465,17 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S41" t="n">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_40.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4564,28 +4564,28 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.36</v>
       </c>
       <c r="Q42" t="n">
         <v>0.25</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S42" t="n">
@@ -4598,7 +4598,7 @@
         <v>1</v>
       </c>
       <c r="V42" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="W42" t="n">
         <v>16</v>
@@ -4633,12 +4633,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_35.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_30.jpg</t>
+          <t>stimuli/fish/fish_39.jpg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4673,18 +4673,18 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0.31</v>
+        <v>0.58</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S43" t="n">
@@ -4697,10 +4697,10 @@
         <v>4</v>
       </c>
       <c r="V43" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="W43" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_39.jpg</t>
+          <t>stimuli/pencil/pencil_35.jpg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4767,19 +4767,19 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P44" t="n">
         <v>0.53</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>3</v>
       </c>
       <c r="W44" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -4930,12 +4930,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_14.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_26.jpg</t>
+          <t>stimuli/key/key_19.jpg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4974,10 +4974,10 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.58</v>
+        <v>0.33</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
@@ -4994,10 +4994,10 @@
         <v>7</v>
       </c>
       <c r="V46" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W46" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_35.jpg</t>
+          <t>stimuli/fish/fish_39.jpg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5054,33 +5054,33 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P47" t="n">
         <v>0.75</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S47" t="n">
@@ -5096,7 +5096,7 @@
         <v>8</v>
       </c>
       <c r="W47" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48">
@@ -5128,12 +5128,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_07.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5148,38 +5148,38 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0.75</v>
+        <v>0.33</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S48" t="n">
@@ -5192,10 +5192,10 @@
         <v>9</v>
       </c>
       <c r="V48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W48" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
@@ -5262,12 +5262,12 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_07.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5366,18 +5366,18 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P50" t="n">
         <v>0.6</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S50" t="n">
@@ -5393,7 +5393,7 @@
         <v>15</v>
       </c>
       <c r="W50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/phone/phone_30.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/jacket/jacket_07.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5460,19 +5460,19 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
@@ -5489,10 +5489,10 @@
         <v>2</v>
       </c>
       <c r="V51" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="W51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_30.jpg</t>
+          <t>stimuli/key/key_19.jpg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_14.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5544,17 +5544,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5564,18 +5564,18 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S52" t="n">
@@ -5588,10 +5588,10 @@
         <v>12</v>
       </c>
       <c r="V52" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W52" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/key/key_19.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_40.jpg</t>
+          <t>stimuli/phone/phone_30.jpg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5658,19 +5658,19 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.53</v>
+        <v>0.26</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
@@ -5687,10 +5687,10 @@
         <v>16</v>
       </c>
       <c r="V53" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="W53" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5747,17 +5747,17 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5769,11 +5769,11 @@
         <v>0.64</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S54" t="n">
@@ -5789,7 +5789,7 @@
         <v>10</v>
       </c>
       <c r="W54" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>stimuli/key/key_11.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -5861,18 +5861,18 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P55" t="n">
         <v>0.8</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S55" t="n">
@@ -5888,7 +5888,7 @@
         <v>3</v>
       </c>
       <c r="W55" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_38.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5964,14 +5964,14 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="Q56" t="n">
         <v>0.31</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S56" t="n">
@@ -5984,7 +5984,7 @@
         <v>3</v>
       </c>
       <c r="V56" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="W56" t="n">
         <v>13</v>
@@ -6019,12 +6019,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_49.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6039,12 +6039,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6054,19 +6054,19 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
@@ -6083,10 +6083,10 @@
         <v>5</v>
       </c>
       <c r="V57" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="W57" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58">
@@ -6118,12 +6118,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6138,38 +6138,38 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.42</v>
+        <v>0.58</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S58" t="n">
@@ -6182,10 +6182,10 @@
         <v>10</v>
       </c>
       <c r="V58" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W58" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>stimuli/key/key_11.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6252,19 +6252,19 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P59" t="n">
         <v>0.8</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>1</v>
       </c>
       <c r="W59" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
@@ -6346,17 +6346,17 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S60" t="n">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/key/key_11.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_10.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6435,17 +6435,17 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6455,18 +6455,18 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0.64</v>
+        <v>0.47</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.47</v>
+        <v>0.2</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S61" t="n">
@@ -6479,10 +6479,10 @@
         <v>2</v>
       </c>
       <c r="V61" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W61" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62">
@@ -6514,14 +6514,14 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_21.jpg</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
           <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_29.jpg</t>
-        </is>
-      </c>
       <c r="I62" t="inlineStr">
         <is>
           <t>bicycle</t>
@@ -6534,38 +6534,38 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
           <t>glasses</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P62" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Q62" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0.27</v>
-      </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S62" t="n">
@@ -6578,10 +6578,10 @@
         <v>9</v>
       </c>
       <c r="V62" t="n">
+        <v>4</v>
+      </c>
+      <c r="W62" t="n">
         <v>18</v>
-      </c>
-      <c r="W62" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="63">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -6653,18 +6653,18 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0.47</v>
+        <v>0.67</v>
       </c>
       <c r="Q63" t="n">
         <v>0.27</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S63" t="n">
@@ -6677,7 +6677,7 @@
         <v>7</v>
       </c>
       <c r="V63" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="W63" t="n">
         <v>8</v>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_10.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6742,28 +6742,28 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="Q64" t="n">
         <v>0.27</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S64" t="n">
@@ -6776,7 +6776,7 @@
         <v>4</v>
       </c>
       <c r="V64" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="W64" t="n">
         <v>1</v>
@@ -6811,12 +6811,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_26.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_38.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6831,38 +6831,38 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.4</v>
+        <v>0.53</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S65" t="n">
@@ -6875,10 +6875,10 @@
         <v>15</v>
       </c>
       <c r="V65" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W65" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6930,38 +6930,38 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0.67</v>
+        <v>0.4</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S66" t="n">
@@ -6974,10 +6974,10 @@
         <v>13</v>
       </c>
       <c r="V66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W66" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_31.jpg</t>
+          <t>stimuli/hammer/hammer_38.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7039,28 +7039,28 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0.42</v>
+        <v>0.58</v>
       </c>
       <c r="Q67" t="n">
         <v>0.2</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S67" t="n">
@@ -7073,7 +7073,7 @@
         <v>15</v>
       </c>
       <c r="V67" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W67" t="n">
         <v>16</v>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_26.jpg</t>
+          <t>stimuli/fish/fish_39.jpg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7155,7 +7155,7 @@
         <v>0.53</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>9</v>
       </c>
       <c r="W68" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_39.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7227,17 +7227,17 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7247,18 +7247,18 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0.47</v>
+        <v>0.64</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S69" t="n">
@@ -7271,10 +7271,10 @@
         <v>4</v>
       </c>
       <c r="V69" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W69" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -7306,12 +7306,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_38.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_35.jpg</t>
+          <t>stimuli/fish/fish_39.jpg</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -7326,38 +7326,38 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0.75</v>
+        <v>0.53</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S70" t="n">
@@ -7370,10 +7370,10 @@
         <v>10</v>
       </c>
       <c r="V70" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="W70" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71">
@@ -7405,12 +7405,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_14.jpg</t>
+          <t>stimuli/hammer/hammer_38.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_39.jpg</t>
+          <t>stimuli/hand/hand_31.jpg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7440,19 +7440,19 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.47</v>
+        <v>0.64</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
@@ -7469,10 +7469,10 @@
         <v>6</v>
       </c>
       <c r="V71" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W71" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72">
@@ -7534,17 +7534,17 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P72" t="n">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S72" t="n">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_39.jpg</t>
+          <t>stimuli/key/key_19.jpg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_07.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7623,17 +7623,17 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -7643,18 +7643,18 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0.58</v>
+        <v>0.4</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S73" t="n">
@@ -7667,10 +7667,10 @@
         <v>5</v>
       </c>
       <c r="V73" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W73" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_26.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7732,28 +7732,28 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="Q74" t="n">
         <v>0.2</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S74" t="n">
@@ -7766,7 +7766,7 @@
         <v>9</v>
       </c>
       <c r="V74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W74" t="n">
         <v>6</v>
@@ -7801,12 +7801,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_12.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_38.jpg</t>
+          <t>stimuli/jacket/jacket_07.jpg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7821,38 +7821,38 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S75" t="n">
@@ -7865,10 +7865,10 @@
         <v>8</v>
       </c>
       <c r="V75" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W75" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>stimuli/key/key_19.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_40.jpg</t>
+          <t>stimuli/pencil/pencil_35.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7920,38 +7920,38 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.33</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S76" t="n">
@@ -7964,10 +7964,10 @@
         <v>3</v>
       </c>
       <c r="V76" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="W76" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_07.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8024,17 +8024,17 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -8046,11 +8046,11 @@
         <v>0.73</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.47</v>
+        <v>0.6</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S77" t="n">
@@ -8066,7 +8066,7 @@
         <v>17</v>
       </c>
       <c r="W77" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8123,12 +8123,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -8138,18 +8138,18 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P78" t="n">
         <v>0.73</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S78" t="n">
@@ -8165,7 +8165,7 @@
         <v>15</v>
       </c>
       <c r="W78" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_12.jpg</t>
+          <t>stimuli/hammer/hammer_38.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_14.jpg</t>
+          <t>stimuli/phone/phone_30.jpg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8217,38 +8217,38 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0.67</v>
+        <v>0.47</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.4</v>
+        <v>0.26</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S79" t="n">
@@ -8261,10 +8261,10 @@
         <v>16</v>
       </c>
       <c r="V79" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W79" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80">
@@ -8296,12 +8296,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>stimuli/key/key_11.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -8316,17 +8316,17 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -8336,18 +8336,18 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S80" t="n">
@@ -8360,10 +8360,10 @@
         <v>16</v>
       </c>
       <c r="V80" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W80" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81">
@@ -8395,12 +8395,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -8415,38 +8415,38 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0.8</v>
+        <v>0.47</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.42</v>
+        <v>0.31</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S81" t="n">
@@ -8459,10 +8459,10 @@
         <v>6</v>
       </c>
       <c r="V81" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W81" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>stimuli/key/key_11.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8519,17 +8519,17 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -8541,11 +8541,11 @@
         <v>0.58</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.36</v>
+        <v>0.47</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S82" t="n">
@@ -8561,7 +8561,7 @@
         <v>2</v>
       </c>
       <c r="W82" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
@@ -8593,7 +8593,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_29.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8628,16 +8628,16 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0.8</v>
+        <v>0.47</v>
       </c>
       <c r="Q83" t="n">
         <v>0.36</v>
@@ -8657,7 +8657,7 @@
         <v>5</v>
       </c>
       <c r="V83" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="W83" t="n">
         <v>13</v>
@@ -8692,7 +8692,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -8732,18 +8732,18 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q84" t="n">
         <v>0.33</v>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S84" t="n">
@@ -8756,7 +8756,7 @@
         <v>10</v>
       </c>
       <c r="V84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W84" t="n">
         <v>18</v>
@@ -8791,12 +8791,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8811,12 +8811,12 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -8826,19 +8826,19 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="R85" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         <v>8</v>
       </c>
       <c r="V85" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="W85" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="86">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8920,12 +8920,12 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -8934,14 +8934,14 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0.64</v>
+        <v>0.4</v>
       </c>
       <c r="Q86" t="n">
         <v>0.2</v>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S86" t="n">
@@ -8954,7 +8954,7 @@
         <v>1</v>
       </c>
       <c r="V86" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="W86" t="n">
         <v>5</v>
@@ -8989,12 +8989,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_10.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0.47</v>
+        <v>0.58</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="R87" t="inlineStr">
         <is>
@@ -9053,10 +9053,10 @@
         <v>2</v>
       </c>
       <c r="V87" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="W87" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -9128,18 +9128,18 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0.4</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q88" t="n">
         <v>0.2</v>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S88" t="n">
@@ -9152,7 +9152,7 @@
         <v>9</v>
       </c>
       <c r="V88" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="W88" t="n">
         <v>8</v>
@@ -9187,12 +9187,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -9207,38 +9207,38 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S89" t="n">
@@ -9251,10 +9251,10 @@
         <v>7</v>
       </c>
       <c r="V89" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="W89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_10.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -9306,38 +9306,38 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.53</v>
+        <v>0.27</v>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S90" t="n">
@@ -9350,10 +9350,10 @@
         <v>4</v>
       </c>
       <c r="V90" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -9425,18 +9425,18 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="Q91" t="n">
         <v>0.4</v>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S91" t="n">
@@ -9449,7 +9449,7 @@
         <v>15</v>
       </c>
       <c r="V91" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="W91" t="n">
         <v>8</v>
@@ -9583,7 +9583,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -9623,18 +9623,18 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0.36</v>
+        <v>0.53</v>
       </c>
       <c r="Q93" t="n">
         <v>0.2</v>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S93" t="n">
@@ -9647,7 +9647,7 @@
         <v>15</v>
       </c>
       <c r="V93" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W93" t="n">
         <v>16</v>
@@ -9682,12 +9682,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_31.jpg</t>
+          <t>stimuli/jacket/jacket_07.jpg</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_39.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9702,17 +9702,17 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -9722,18 +9722,18 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0.47</v>
+        <v>0.75</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S94" t="n">
@@ -9746,10 +9746,10 @@
         <v>1</v>
       </c>
       <c r="V94" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W94" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_38.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_26.jpg</t>
+          <t>stimuli/pencil/pencil_35.jpg</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -9825,10 +9825,10 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.42</v>
+        <v>0.31</v>
       </c>
       <c r="R95" t="inlineStr">
         <is>
@@ -9845,10 +9845,10 @@
         <v>4</v>
       </c>
       <c r="V95" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W95" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96">
@@ -9885,7 +9885,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_35.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9905,17 +9905,17 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -9927,11 +9927,11 @@
         <v>0.64</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.36</v>
+        <v>0.47</v>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S96" t="n">
@@ -9947,7 +9947,7 @@
         <v>9</v>
       </c>
       <c r="W96" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_14.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_31.jpg</t>
+          <t>stimuli/fish/fish_39.jpg</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -9999,17 +9999,17 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -10019,18 +10019,18 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0.75</v>
+        <v>0.58</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.64</v>
+        <v>0.47</v>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S97" t="n">
@@ -10043,10 +10043,10 @@
         <v>6</v>
       </c>
       <c r="V97" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W97" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="98">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_30.jpg</t>
+          <t>stimuli/hand/hand_31.jpg</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -10113,19 +10113,19 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0.4</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.27</v>
+        <v>0.58</v>
       </c>
       <c r="R98" t="inlineStr">
         <is>
@@ -10142,10 +10142,10 @@
         <v>7</v>
       </c>
       <c r="V98" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="W98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_31.jpg</t>
+          <t>stimuli/phone/phone_30.jpg</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_12.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -10197,17 +10197,17 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -10217,18 +10217,18 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0.75</v>
+        <v>0.47</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S99" t="n">
@@ -10241,10 +10241,10 @@
         <v>5</v>
       </c>
       <c r="V99" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="W99" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_07.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -10296,12 +10296,12 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -10311,19 +10311,19 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="R100" t="inlineStr">
         <is>
@@ -10340,10 +10340,10 @@
         <v>9</v>
       </c>
       <c r="V100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W100" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_40.jpg</t>
+          <t>stimuli/hammer/hammer_38.jpg</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -10400,33 +10400,33 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P101" t="n">
         <v>0.4</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S101" t="n">
@@ -10442,7 +10442,7 @@
         <v>4</v>
       </c>
       <c r="W101" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102">
@@ -10504,17 +10504,17 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P102" t="n">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S102" t="n">
@@ -10573,12 +10573,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_30.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_40.jpg</t>
+          <t>stimuli/hammer/hammer_38.jpg</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -10593,38 +10593,38 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0.73</v>
+        <v>0.53</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S103" t="n">
@@ -10637,10 +10637,10 @@
         <v>2</v>
       </c>
       <c r="V103" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="W103" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104">
@@ -10672,12 +10672,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>stimuli/key/key_19.jpg</t>
+          <t>stimuli/phone/phone_30.jpg</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_14.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -10692,22 +10692,22 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -10716,14 +10716,14 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S104" t="n">
@@ -10736,10 +10736,10 @@
         <v>12</v>
       </c>
       <c r="V104" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W104" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="105">
@@ -10771,12 +10771,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/key/key_19.jpg</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_40.jpg</t>
+          <t>stimuli/jacket/jacket_07.jpg</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -10806,19 +10806,19 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="Q105" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="R105" t="inlineStr">
         <is>
@@ -10835,10 +10835,10 @@
         <v>16</v>
       </c>
       <c r="V105" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="W105" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/psychopy_exp_files/sequences/learning_block3_fixed-middle-10_12.xlsx
+++ b/psychopy_exp_files/sequences/learning_block3_fixed-middle-10_12.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>16</v>
       </c>
       <c r="V2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W2" t="n">
         <v>13</v>
@@ -668,7 +668,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -734,7 +734,7 @@
         <v>16</v>
       </c>
       <c r="U3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V3" t="n">
         <v>7</v>
@@ -762,14 +762,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_21.jpg</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_04.jpg</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>stimuli/ball/ball_37.jpg</t>
@@ -782,12 +782,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -830,10 +830,10 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
         <v>6</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3</v>
       </c>
       <c r="V4" t="n">
         <v>1</v>
@@ -861,42 +861,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>stimuli/house/house_30.jpg</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_49.jpg</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_21.jpg</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>chair</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -929,16 +929,16 @@
         <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V5" t="n">
         <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -960,7 +960,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1028,7 +1028,7 @@
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U6" t="n">
         <v>10</v>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1136,7 +1136,7 @@
         <v>18</v>
       </c>
       <c r="W7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1235,7 +1235,7 @@
         <v>16</v>
       </c>
       <c r="W8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -1361,12 +1361,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1381,12 +1381,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1427,10 +1427,10 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="V10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W10" t="n">
         <v>8</v>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1523,13 +1523,13 @@
         <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
         <v>7</v>
       </c>
       <c r="V11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W11" t="n">
         <v>13</v>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1625,10 +1625,10 @@
         <v>7</v>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W12" t="n">
         <v>8</v>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1721,7 +1721,7 @@
         <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U13" t="n">
         <v>15</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1925,7 +1925,7 @@
         <v>15</v>
       </c>
       <c r="V15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W15" t="n">
         <v>16</v>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_40.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2024,7 +2024,7 @@
         <v>1</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W16" t="n">
         <v>2</v>
@@ -2054,12 +2054,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_12.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2074,12 +2074,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2120,10 +2120,10 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W17" t="n">
         <v>12</v>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_12.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2216,13 +2216,13 @@
         <v>5</v>
       </c>
       <c r="T18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U18" t="n">
         <v>10</v>
       </c>
       <c r="V18" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W18" t="n">
         <v>16</v>
@@ -2252,12 +2252,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_40.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_14.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2272,12 +2272,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2318,10 +2318,10 @@
         <v>10</v>
       </c>
       <c r="U19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V19" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W19" t="n">
         <v>12</v>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_40.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2414,7 +2414,7 @@
         <v>7</v>
       </c>
       <c r="T20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U20" t="n">
         <v>7</v>
@@ -2450,19 +2450,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>stimuli/house/house_37.jpg</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_48.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_37.jpg</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_12.jpg</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>hammer</t>
@@ -2470,17 +2470,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>chair</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2516,13 +2516,13 @@
         <v>7</v>
       </c>
       <c r="U21" t="n">
+        <v>9</v>
+      </c>
+      <c r="V21" t="n">
+        <v>3</v>
+      </c>
+      <c r="W21" t="n">
         <v>5</v>
-      </c>
-      <c r="V21" t="n">
-        <v>9</v>
-      </c>
-      <c r="W21" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_14.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2612,10 +2612,10 @@
         <v>9</v>
       </c>
       <c r="T22" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U22" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="V22" t="n">
         <v>8</v>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_40.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2711,7 +2711,7 @@
         <v>10</v>
       </c>
       <c r="T23" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
         <v>8</v>
@@ -2720,7 +2720,7 @@
         <v>1</v>
       </c>
       <c r="W23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2813,7 +2813,7 @@
         <v>8</v>
       </c>
       <c r="U24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V24" t="n">
         <v>17</v>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2856,12 +2856,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_12.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2909,7 +2909,7 @@
         <v>12</v>
       </c>
       <c r="T25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U25" t="n">
         <v>2</v>
@@ -2918,7 +2918,7 @@
         <v>15</v>
       </c>
       <c r="W25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_12.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3014,7 +3014,7 @@
         <v>12</v>
       </c>
       <c r="V26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W26" t="n">
         <v>7</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_40.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3116,7 +3116,7 @@
         <v>15</v>
       </c>
       <c r="W27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3212,7 +3212,7 @@
         <v>16</v>
       </c>
       <c r="V28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W28" t="n">
         <v>13</v>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3308,7 +3308,7 @@
         <v>16</v>
       </c>
       <c r="U29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V29" t="n">
         <v>10</v>
@@ -3336,14 +3336,14 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_21.jpg</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_04.jpg</t>
-        </is>
-      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>stimuli/hand/hand_38.jpg</t>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3404,10 +3404,10 @@
         <v>4</v>
       </c>
       <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
         <v>6</v>
-      </c>
-      <c r="U30" t="n">
-        <v>3</v>
       </c>
       <c r="V30" t="n">
         <v>8</v>
@@ -3435,12 +3435,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3503,10 +3503,10 @@
         <v>5</v>
       </c>
       <c r="T31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U31" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V31" t="n">
         <v>10</v>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3602,7 +3602,7 @@
         <v>6</v>
       </c>
       <c r="T32" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U32" t="n">
         <v>10</v>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3707,7 +3707,7 @@
         <v>8</v>
       </c>
       <c r="V33" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W33" t="n">
         <v>15</v>
@@ -3742,12 +3742,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3806,10 +3806,10 @@
         <v>1</v>
       </c>
       <c r="V34" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W34" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4001,13 +4001,13 @@
         <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="V36" t="n">
         <v>16</v>
       </c>
       <c r="W36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4097,13 +4097,13 @@
         <v>11</v>
       </c>
       <c r="T37" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
         <v>7</v>
       </c>
       <c r="V37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W37" t="n">
         <v>13</v>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -4199,7 +4199,7 @@
         <v>7</v>
       </c>
       <c r="U38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V38" t="n">
         <v>13</v>
@@ -4227,19 +4227,19 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_36.jpg</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>stimuli/key/key_11.jpg</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>stimuli/key/key_11.jpg</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_07.jpg</t>
-        </is>
-      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>stimuli/ball/ball_37.jpg</t>
@@ -4247,17 +4247,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4295,13 +4295,13 @@
         <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U39" t="n">
         <v>15</v>
       </c>
       <c r="V39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W39" t="n">
         <v>1</v>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4400,7 +4400,7 @@
         <v>13</v>
       </c>
       <c r="V40" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W40" t="n">
         <v>18</v>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_12.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4499,7 +4499,7 @@
         <v>15</v>
       </c>
       <c r="V41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W41" t="n">
         <v>12</v>
@@ -4628,12 +4628,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_12.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4694,10 +4694,10 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V43" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W43" t="n">
         <v>12</v>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_12.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4790,13 +4790,13 @@
         <v>5</v>
       </c>
       <c r="T44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U44" t="n">
         <v>10</v>
       </c>
       <c r="V44" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W44" t="n">
         <v>16</v>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_40.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4892,7 +4892,7 @@
         <v>10</v>
       </c>
       <c r="U45" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V45" t="n">
         <v>17</v>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_40.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4988,13 +4988,13 @@
         <v>7</v>
       </c>
       <c r="T46" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U46" t="n">
         <v>7</v>
       </c>
       <c r="V46" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W46" t="n">
         <v>15</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_14.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -5090,7 +5090,7 @@
         <v>7</v>
       </c>
       <c r="U47" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V47" t="n">
         <v>8</v>
@@ -5118,42 +5118,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>stimuli/house/house_37.jpg</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_48.jpg</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_37.jpg</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_40.jpg</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5186,16 +5186,16 @@
         <v>9</v>
       </c>
       <c r="T48" t="n">
+        <v>9</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
+      </c>
+      <c r="V48" t="n">
         <v>5</v>
       </c>
-      <c r="U48" t="n">
-        <v>9</v>
-      </c>
-      <c r="V48" t="n">
+      <c r="W48" t="n">
         <v>4</v>
-      </c>
-      <c r="W48" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="49">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5285,7 +5285,7 @@
         <v>10</v>
       </c>
       <c r="T49" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U49" t="n">
         <v>8</v>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_14.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5387,13 +5387,13 @@
         <v>8</v>
       </c>
       <c r="U50" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V50" t="n">
         <v>15</v>
       </c>
       <c r="W50" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5483,7 +5483,7 @@
         <v>12</v>
       </c>
       <c r="T51" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U51" t="n">
         <v>2</v>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5591,7 +5591,7 @@
         <v>15</v>
       </c>
       <c r="W52" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_14.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5687,7 +5687,7 @@
         <v>16</v>
       </c>
       <c r="V53" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W53" t="n">
         <v>17</v>
@@ -5816,17 +5816,17 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_21.jpg</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_04.jpg</t>
-        </is>
-      </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5836,17 +5836,17 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5882,13 +5882,13 @@
         <v>16</v>
       </c>
       <c r="U55" t="n">
+        <v>4</v>
+      </c>
+      <c r="V55" t="n">
         <v>6</v>
       </c>
-      <c r="V55" t="n">
-        <v>3</v>
-      </c>
       <c r="W55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -5910,14 +5910,14 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_21.jpg</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_04.jpg</t>
-        </is>
-      </c>
       <c r="G56" t="inlineStr">
         <is>
           <t>stimuli/bicycle/bicycle_49.jpg</t>
@@ -5930,12 +5930,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5978,10 +5978,10 @@
         <v>4</v>
       </c>
       <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
         <v>6</v>
-      </c>
-      <c r="U56" t="n">
-        <v>3</v>
       </c>
       <c r="V56" t="n">
         <v>2</v>
@@ -6009,19 +6009,19 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_07.jpg</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_30.jpg</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_36.jpg</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_30.jpg</t>
-        </is>
-      </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>stimuli/key/key_11.jpg</t>
@@ -6029,17 +6029,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>house</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6077,13 +6077,13 @@
         <v>5</v>
       </c>
       <c r="T57" t="n">
+        <v>6</v>
+      </c>
+      <c r="U57" t="n">
+        <v>9</v>
+      </c>
+      <c r="V57" t="n">
         <v>3</v>
-      </c>
-      <c r="U57" t="n">
-        <v>5</v>
-      </c>
-      <c r="V57" t="n">
-        <v>9</v>
       </c>
       <c r="W57" t="n">
         <v>15</v>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6176,7 +6176,7 @@
         <v>6</v>
       </c>
       <c r="T58" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U58" t="n">
         <v>10</v>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6284,7 +6284,7 @@
         <v>1</v>
       </c>
       <c r="W59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6380,10 +6380,10 @@
         <v>1</v>
       </c>
       <c r="V60" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W60" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6575,10 +6575,10 @@
         <v>2</v>
       </c>
       <c r="U62" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="V62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W62" t="n">
         <v>18</v>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6671,7 +6671,7 @@
         <v>11</v>
       </c>
       <c r="T63" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U63" t="n">
         <v>7</v>
@@ -6707,14 +6707,14 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_36.jpg</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_07.jpg</t>
-        </is>
-      </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>stimuli/ball/ball_37.jpg</t>
@@ -6727,12 +6727,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6773,10 +6773,10 @@
         <v>7</v>
       </c>
       <c r="U64" t="n">
+        <v>5</v>
+      </c>
+      <c r="V64" t="n">
         <v>4</v>
-      </c>
-      <c r="V64" t="n">
-        <v>6</v>
       </c>
       <c r="W64" t="n">
         <v>1</v>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6869,7 +6869,7 @@
         <v>13</v>
       </c>
       <c r="T65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U65" t="n">
         <v>15</v>
@@ -6878,7 +6878,7 @@
         <v>16</v>
       </c>
       <c r="W65" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7172,7 +7172,7 @@
         <v>1</v>
       </c>
       <c r="V68" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W68" t="n">
         <v>12</v>
@@ -7202,12 +7202,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_12.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_14.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7268,10 +7268,10 @@
         <v>1</v>
       </c>
       <c r="U69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V69" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W69" t="n">
         <v>2</v>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_12.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7364,13 +7364,13 @@
         <v>5</v>
       </c>
       <c r="T70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U70" t="n">
         <v>10</v>
       </c>
       <c r="V70" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W70" t="n">
         <v>12</v>
@@ -7400,7 +7400,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_40.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7466,7 +7466,7 @@
         <v>10</v>
       </c>
       <c r="U71" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V71" t="n">
         <v>7</v>
@@ -7494,7 +7494,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_40.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7562,7 +7562,7 @@
         <v>7</v>
       </c>
       <c r="T72" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U72" t="n">
         <v>7</v>
@@ -7598,19 +7598,19 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
+          <t>stimuli/house/house_37.jpg</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>stimuli/key/key_19.jpg</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>stimuli/key/key_19.jpg</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_12.jpg</t>
-        </is>
-      </c>
       <c r="I73" t="inlineStr">
         <is>
           <t>hammer</t>
@@ -7618,17 +7618,17 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>chair</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -7664,13 +7664,13 @@
         <v>7</v>
       </c>
       <c r="U73" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V73" t="n">
         <v>15</v>
       </c>
       <c r="W73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -7692,42 +7692,42 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_14.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_40.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -7760,16 +7760,16 @@
         <v>9</v>
       </c>
       <c r="T74" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U74" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="V74" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W74" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7859,7 +7859,7 @@
         <v>10</v>
       </c>
       <c r="T75" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U75" t="n">
         <v>8</v>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7961,7 +7961,7 @@
         <v>8</v>
       </c>
       <c r="U76" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V76" t="n">
         <v>2</v>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8057,7 +8057,7 @@
         <v>12</v>
       </c>
       <c r="T77" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U77" t="n">
         <v>2</v>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_14.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8165,7 +8165,7 @@
         <v>15</v>
       </c>
       <c r="W78" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8360,7 +8360,7 @@
         <v>16</v>
       </c>
       <c r="V80" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W80" t="n">
         <v>13</v>
@@ -8390,12 +8390,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -8410,12 +8410,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8456,10 +8456,10 @@
         <v>16</v>
       </c>
       <c r="U81" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V81" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W81" t="n">
         <v>15</v>
@@ -8484,14 +8484,14 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_21.jpg</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_04.jpg</t>
-        </is>
-      </c>
       <c r="G82" t="inlineStr">
         <is>
           <t>stimuli/bicycle/bicycle_49.jpg</t>
@@ -8504,12 +8504,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -8552,10 +8552,10 @@
         <v>4</v>
       </c>
       <c r="T82" t="n">
+        <v>4</v>
+      </c>
+      <c r="U82" t="n">
         <v>6</v>
-      </c>
-      <c r="U82" t="n">
-        <v>3</v>
       </c>
       <c r="V82" t="n">
         <v>2</v>
@@ -8583,19 +8583,19 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
+          <t>stimuli/house/house_30.jpg</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_21.jpg</t>
-        </is>
-      </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>stimuli/guitar/guitar_27.jpg</t>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>chair</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8651,13 +8651,13 @@
         <v>5</v>
       </c>
       <c r="T83" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U83" t="n">
+        <v>9</v>
+      </c>
+      <c r="V83" t="n">
         <v>5</v>
-      </c>
-      <c r="V83" t="n">
-        <v>4</v>
       </c>
       <c r="W83" t="n">
         <v>13</v>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -8702,7 +8702,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -8750,7 +8750,7 @@
         <v>6</v>
       </c>
       <c r="T84" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U84" t="n">
         <v>10</v>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -8957,7 +8957,7 @@
         <v>16</v>
       </c>
       <c r="W86" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87">
@@ -8994,7 +8994,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -9056,7 +9056,7 @@
         <v>13</v>
       </c>
       <c r="W87" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
@@ -9083,7 +9083,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -9149,7 +9149,7 @@
         <v>2</v>
       </c>
       <c r="U88" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="V88" t="n">
         <v>15</v>
@@ -9177,7 +9177,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -9245,7 +9245,7 @@
         <v>11</v>
       </c>
       <c r="T89" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U89" t="n">
         <v>7</v>
@@ -9281,7 +9281,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -9347,7 +9347,7 @@
         <v>7</v>
       </c>
       <c r="U90" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V90" t="n">
         <v>18</v>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -9443,7 +9443,7 @@
         <v>13</v>
       </c>
       <c r="T91" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U91" t="n">
         <v>15</v>
@@ -9583,7 +9583,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_14.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -9647,7 +9647,7 @@
         <v>15</v>
       </c>
       <c r="V93" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W93" t="n">
         <v>16</v>
@@ -9776,14 +9776,14 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_14.jpg</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_40.jpg</t>
-        </is>
-      </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>stimuli/pencil/pencil_35.jpg</t>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -9842,10 +9842,10 @@
         <v>1</v>
       </c>
       <c r="U95" t="n">
+        <v>5</v>
+      </c>
+      <c r="V95" t="n">
         <v>4</v>
-      </c>
-      <c r="V95" t="n">
-        <v>6</v>
       </c>
       <c r="W95" t="n">
         <v>16</v>
@@ -9870,7 +9870,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_12.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -9900,7 +9900,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9938,13 +9938,13 @@
         <v>5</v>
       </c>
       <c r="T96" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U96" t="n">
         <v>10</v>
       </c>
       <c r="V96" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W96" t="n">
         <v>2</v>
@@ -9974,14 +9974,14 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_12.jpg</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_48.jpg</t>
-        </is>
-      </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>stimuli/fish/fish_39.jpg</t>
@@ -9994,12 +9994,12 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -10040,10 +10040,10 @@
         <v>10</v>
       </c>
       <c r="U97" t="n">
+        <v>4</v>
+      </c>
+      <c r="V97" t="n">
         <v>6</v>
-      </c>
-      <c r="V97" t="n">
-        <v>3</v>
       </c>
       <c r="W97" t="n">
         <v>12</v>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_40.jpg</t>
+          <t>stimuli/chair/chair_12.jpg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -10136,7 +10136,7 @@
         <v>7</v>
       </c>
       <c r="T98" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U98" t="n">
         <v>7</v>
@@ -10172,7 +10172,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_14.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -10238,7 +10238,7 @@
         <v>7</v>
       </c>
       <c r="U99" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V99" t="n">
         <v>17</v>
@@ -10266,42 +10266,42 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
+          <t>stimuli/house/house_37.jpg</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_48.jpg</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_37.jpg</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_26.jpg</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_12.jpg</t>
-        </is>
-      </c>
       <c r="I100" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>chair</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -10334,16 +10334,16 @@
         <v>9</v>
       </c>
       <c r="T100" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U100" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="V100" t="n">
         <v>2</v>
       </c>
       <c r="W100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_12.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -10433,13 +10433,13 @@
         <v>10</v>
       </c>
       <c r="T101" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U101" t="n">
         <v>8</v>
       </c>
       <c r="V101" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W101" t="n">
         <v>7</v>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -10479,7 +10479,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_12.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -10535,13 +10535,13 @@
         <v>8</v>
       </c>
       <c r="U102" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V102" t="n">
         <v>15</v>
       </c>
       <c r="W102" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_48.jpg</t>
+          <t>stimuli/flower/flower_40.jpg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_12.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -10631,13 +10631,13 @@
         <v>12</v>
       </c>
       <c r="T103" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U103" t="n">
         <v>2</v>
       </c>
       <c r="V103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W103" t="n">
         <v>7</v>
@@ -10677,7 +10677,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/bread/bread_48.jpg</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -10739,7 +10739,7 @@
         <v>17</v>
       </c>
       <c r="W104" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
